--- a/Manuscript Variant Workbooks/Grec17-to-Holmes155_MS-spreadsheet.xlsx
+++ b/Manuscript Variant Workbooks/Grec17-to-Holmes155_MS-spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/8 Corrections/Files to Upload/To Github/Manuscript Variant Workbooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/10 The Final Final Version/New and Updated Files for Upload/MS Variant Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="13_ncr:1_{E86589DA-4926-41B0-8A12-72B1132EB0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF7A3B5-8B46-4E1F-A4A5-D6AB7D0F8352}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="13_ncr:1_{E86589DA-4926-41B0-8A12-72B1132EB0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1502AFE-C2B8-4BFF-BE70-D2CD81FEA23F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5BB4D106-A247-41F8-A104-83D51E35EC09}"/>
+    <workbookView xWindow="-19530" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{5BB4D106-A247-41F8-A104-83D51E35EC09}"/>
   </bookViews>
   <sheets>
     <sheet name="Unfiltered Data" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">AddOmits!$A$1:$AF$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gen-filters'!$A$1:$AE$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unfiltered Data'!$A$1:$AI$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unfiltered Data'!$A$1:$AI$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4201,6 +4201,15 @@
     <author>tc={F7CC5031-C068-4958-9291-A0EA6D93DBBB}</author>
     <author>tc={43A919E2-9981-4DD9-AD96-4601D145ADFC}</author>
     <author>tc={FEC708A9-70FD-4C58-AB27-F6C8F344E5A0}</author>
+    <author>tc={029302B5-8DBB-43C1-9EAE-57435D570271}</author>
+    <author>tc={033D2352-830B-4F03-BEF8-A0B47D67F01B}</author>
+    <author>tc={850EFAD6-186B-42E2-A8D1-E7DAD3953233}</author>
+    <author>tc={FE5C4ADC-A547-45B8-B2A8-B93F887DDA67}</author>
+    <author>tc={56E4F678-7AAD-445E-8548-9623DD5B6130}</author>
+    <author>tc={EDD45899-D5CA-478D-B216-EF02AD0A7A01}</author>
+    <author>tc={9E83E2FE-0BEE-4B54-A372-E2FC83FFBB49}</author>
+    <author>tc={581DA618-F2EF-46AC-8A52-5DEE2D657BB1}</author>
+    <author>tc={2DA9BCD1-192C-4951-9ABE-3CB3A1F49991}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C2E6C457-B212-4BA6-BEB2-55CBC799643B}">
@@ -4606,7 +4615,7 @@
     For substitutions, the word frequency of the autograph reading</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{FA387B5E-2B50-43F7-A811-E2AA8E4F5F40}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{FA387B5E-2B50-43F7-A811-E2AA8E4F5F40}">
       <text>
         <r>
           <rPr>
@@ -4630,7 +4639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{84084412-AEBF-441E-9F85-4753A88BC536}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{84084412-AEBF-441E-9F85-4753A88BC536}">
       <text>
         <r>
           <rPr>
@@ -4654,7 +4663,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{F0F0113B-81E9-42FD-BAC4-45A03BF26208}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{F0F0113B-81E9-42FD-BAC4-45A03BF26208}">
       <text>
         <r>
           <rPr>
@@ -4678,7 +4687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{EC4E93B6-B9C6-4E80-AEDC-959DA33BA95A}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{EC4E93B6-B9C6-4E80-AEDC-959DA33BA95A}">
       <text>
         <r>
           <rPr>
@@ -4702,7 +4711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{F5DF567A-2D6E-48B8-B819-AB70A4838B07}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{F5DF567A-2D6E-48B8-B819-AB70A4838B07}">
       <text>
         <r>
           <rPr>
@@ -4727,7 +4736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{7F259A1D-D5DE-4200-998B-252A84FE6FA3}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{7F259A1D-D5DE-4200-998B-252A84FE6FA3}">
       <text>
         <r>
           <rPr>
@@ -4751,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{D08E0457-A35A-49A8-AEC7-3F5946DC2646}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{D08E0457-A35A-49A8-AEC7-3F5946DC2646}">
       <text>
         <r>
           <rPr>
@@ -4775,7 +4784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="3" shapeId="0" xr:uid="{F7CC5031-C068-4958-9291-A0EA6D93DBBB}">
+    <comment ref="D21" authorId="3" shapeId="0" xr:uid="{F7CC5031-C068-4958-9291-A0EA6D93DBBB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4783,7 +4792,7 @@
     The number of variants that harmonized to parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D21" authorId="4" shapeId="0" xr:uid="{43A919E2-9981-4DD9-AD96-4601D145ADFC}">
+    <comment ref="D22" authorId="4" shapeId="0" xr:uid="{43A919E2-9981-4DD9-AD96-4601D145ADFC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4791,7 +4800,79 @@
     The number of variants that disharmonized from  parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D22" authorId="5" shapeId="0" xr:uid="{FEC708A9-70FD-4C58-AB27-F6C8F344E5A0}">
+    <comment ref="D23" authorId="5" shapeId="0" xr:uid="{FEC708A9-70FD-4C58-AB27-F6C8F344E5A0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</t>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="6" shapeId="0" xr:uid="{029302B5-8DBB-43C1-9EAE-57435D570271}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="7" shapeId="0" xr:uid="{033D2352-830B-4F03-BEF8-A0B47D67F01B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="8" shapeId="0" xr:uid="{850EFAD6-186B-42E2-A8D1-E7DAD3953233}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="9" shapeId="0" xr:uid="{FE5C4ADC-A547-45B8-B2A8-B93F887DDA67}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="10" shapeId="0" xr:uid="{56E4F678-7AAD-445E-8548-9623DD5B6130}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</t>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="11" shapeId="0" xr:uid="{EDD45899-D5CA-478D-B216-EF02AD0A7A01}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All potential cases of verbal harmonization/disharmonization, forward and backward.</t>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="12" shapeId="0" xr:uid="{9E83E2FE-0BEE-4B54-A372-E2FC83FFBB49}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that harmonized to parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="13" shapeId="0" xr:uid="{581DA618-F2EF-46AC-8A52-5DEE2D657BB1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that disharmonized from  parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="14" shapeId="0" xr:uid="{2DA9BCD1-192C-4951-9ABE-3CB3A1F49991}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4963,7 +5044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{A1C5332B-88AA-4B83-AAD9-A3B93A9071E6}">
+    <comment ref="L3" authorId="1" shapeId="0" xr:uid="{A1C5332B-88AA-4B83-AAD9-A3B93A9071E6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4971,7 +5052,7 @@
     The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</t>
       </text>
     </comment>
-    <comment ref="K4" authorId="2" shapeId="0" xr:uid="{1B9938A4-1C03-4D8C-9F9D-9A6F1DAD277F}">
+    <comment ref="L4" authorId="2" shapeId="0" xr:uid="{1B9938A4-1C03-4D8C-9F9D-9A6F1DAD277F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4979,7 +5060,7 @@
     That is, the autograph contains a singular reading and the apograph followed it</t>
       </text>
     </comment>
-    <comment ref="K5" authorId="3" shapeId="0" xr:uid="{F80E6062-5FB5-40A2-84DD-622A30330BE2}">
+    <comment ref="L5" authorId="3" shapeId="0" xr:uid="{F80E6062-5FB5-40A2-84DD-622A30330BE2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -4987,7 +5068,7 @@
     The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="4" shapeId="0" xr:uid="{6A36EA43-D646-40E2-B193-E1084727A5A3}">
+    <comment ref="N13" authorId="4" shapeId="0" xr:uid="{6A36EA43-D646-40E2-B193-E1084727A5A3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -5000,7 +5081,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3110" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3153" uniqueCount="746">
   <si>
     <t>Verse Ref</t>
   </si>
@@ -7602,6 +7683,36 @@
   </si>
   <si>
     <t>dropped the article and wrote the wrong numeral; autograph reading matches the pattern seen in Lev 29:20,23,26,32 of τη ημερα τη &lt;numeral&gt;; apograph disharmonizes</t>
+  </si>
+  <si>
+    <t>Harmonization_Direction</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Backward</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Directionality</t>
+  </si>
+  <si>
+    <t>Forward (Exclusive)</t>
+  </si>
+  <si>
+    <t>Forward (Inclusive)</t>
+  </si>
+  <si>
+    <t>Backward (Exclusive)</t>
+  </si>
+  <si>
+    <t>Backward (Inclusive)</t>
+  </si>
+  <si>
+    <t>Matches pattern in v. 26 (επι τα δυο πτερυγια)</t>
   </si>
 </sst>
 </file>
@@ -7727,22 +7838,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="219">
+  <dxfs count="233">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -7796,8 +7896,19 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -7809,6 +7920,17 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -7862,8 +7984,129 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -7930,6 +8173,24 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -8384,17 +8645,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -8407,17 +8657,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -8460,6 +8699,28 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
@@ -8482,8 +8743,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -8559,6 +8820,17 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
@@ -8581,17 +8853,17 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
       <border>
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -8635,8 +8907,106 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
       <border>
@@ -8669,28 +9039,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border>
@@ -8733,96 +9082,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border>
@@ -8898,6 +9159,17 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
@@ -8920,17 +9192,17 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
       <border>
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -8974,8 +9246,106 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
       <border>
@@ -9008,28 +9378,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border>
@@ -9072,96 +9421,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border>
@@ -9237,6 +9498,17 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
@@ -9259,17 +9531,17 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
       <border>
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -9313,30 +9585,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -9354,14 +9604,25 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -10574,13 +10835,40 @@
   <threadedComment ref="T1" dT="2024-01-16T09:59:48.08" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{AD328834-B5AD-44BA-B659-EE42B3C3E417}">
     <text>For substitutions, the word frequency of the autograph reading</text>
   </threadedComment>
-  <threadedComment ref="D20" dT="2024-01-24T17:15:11.25" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{F7CC5031-C068-4958-9291-A0EA6D93DBBB}">
+  <threadedComment ref="D21" dT="2024-01-24T17:15:11.25" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{F7CC5031-C068-4958-9291-A0EA6D93DBBB}">
     <text>The number of variants that harmonized to parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D21" dT="2024-01-24T17:15:35.01" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{43A919E2-9981-4DD9-AD96-4601D145ADFC}">
+  <threadedComment ref="D22" dT="2024-01-24T17:15:35.01" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{43A919E2-9981-4DD9-AD96-4601D145ADFC}">
     <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D22" dT="2024-01-24T17:16:15.06" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{FEC708A9-70FD-4C58-AB27-F6C8F344E5A0}">
+  <threadedComment ref="D23" dT="2024-01-24T17:16:15.06" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{FEC708A9-70FD-4C58-AB27-F6C8F344E5A0}">
+    <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
+  </threadedComment>
+  <threadedComment ref="E27" dT="2026-03-27T21:09:00.40" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{029302B5-8DBB-43C1-9EAE-57435D570271}">
+    <text>ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="F27" dT="2026-03-26T18:54:36.97" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{033D2352-830B-4F03-BEF8-A0B47D67F01B}">
+    <text>All cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="G27" dT="2026-03-27T21:09:12.56" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{850EFAD6-186B-42E2-A8D1-E7DAD3953233}">
+    <text>ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="H27" dT="2026-03-26T18:55:05.59" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{FE5C4ADC-A547-45B8-B2A8-B93F887DDA67}">
+    <text>All cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="I27" dT="2026-03-26T18:56:11.72" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{56E4F678-7AAD-445E-8548-9623DD5B6130}">
+    <text>Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</text>
+  </threadedComment>
+  <threadedComment ref="J27" dT="2026-03-26T18:56:36.44" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{EDD45899-D5CA-478D-B216-EF02AD0A7A01}">
+    <text>All potential cases of verbal harmonization/disharmonization, forward and backward.</text>
+  </threadedComment>
+  <threadedComment ref="D28" dT="2024-01-24T17:15:11.25" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{9E83E2FE-0BEE-4B54-A372-E2FC83FFBB49}">
+    <text>The number of variants that harmonized to parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D29" dT="2024-01-24T17:15:35.01" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{581DA618-F2EF-46AC-8A52-5DEE2D657BB1}">
+    <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D30" dT="2024-01-24T17:16:15.06" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{2DA9BCD1-192C-4951-9ABE-3CB3A1F49991}">
     <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
   </threadedComment>
 </ThreadedComments>
@@ -10608,16 +10896,16 @@
 
 <file path=xl/threadedComments/threadedComment9.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K3" dT="2023-08-03T13:34:30.53" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{A1C5332B-88AA-4B83-AAD9-A3B93A9071E6}">
+  <threadedComment ref="L3" dT="2023-08-03T13:34:30.53" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{A1C5332B-88AA-4B83-AAD9-A3B93A9071E6}">
     <text>The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</text>
   </threadedComment>
-  <threadedComment ref="K4" dT="2023-08-03T13:33:28.57" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{1B9938A4-1C03-4D8C-9F9D-9A6F1DAD277F}">
+  <threadedComment ref="L4" dT="2023-08-03T13:33:28.57" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{1B9938A4-1C03-4D8C-9F9D-9A6F1DAD277F}">
     <text>That is, the autograph contains a singular reading and the apograph followed it</text>
   </threadedComment>
-  <threadedComment ref="K5" dT="2023-08-03T13:35:10.13" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{F80E6062-5FB5-40A2-84DD-622A30330BE2}">
+  <threadedComment ref="L5" dT="2023-08-03T13:35:10.13" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{F80E6062-5FB5-40A2-84DD-622A30330BE2}">
     <text>The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</text>
   </threadedComment>
-  <threadedComment ref="M13" dT="2023-08-14T14:21:11.11" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{6A36EA43-D646-40E2-B193-E1084727A5A3}">
+  <threadedComment ref="N13" dT="2023-08-14T14:21:11.11" personId="{92B4A6DC-4F33-4B08-ABD0-0D16C795A856}" id="{6A36EA43-D646-40E2-B193-E1084727A5A3}">
     <text>For words which have multiple common forms not impacting their inflection (e.g., ουκ-ουχ-ου, επι-επ-εφ)</text>
   </threadedComment>
 </ThreadedComments>
@@ -10625,7 +10913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6186005F-94E2-41CC-8345-C084BDDA2E52}">
-  <dimension ref="A1:AI194"/>
+  <dimension ref="A1:AI197"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -11131,6 +11419,9 @@
       <c r="E12" s="3" t="s">
         <v>555</v>
       </c>
+      <c r="I12" t="s">
+        <v>745</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>545</v>
       </c>
@@ -11145,6 +11436,9 @@
       <c r="V12" s="5">
         <f t="shared" ca="1" si="3"/>
         <v>1420</v>
+      </c>
+      <c r="W12" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="AA12" s="5" t="s">
         <v>475</v>
@@ -17269,122 +17563,129 @@
         <v>187</v>
       </c>
     </row>
+    <row r="197" spans="4:5">
+      <c r="E197" s="3">
+        <f>COUNTIF(F:F, "Autograph transcript error, but still a variant") + COUNTIF(F:F, "Apograph transcript error, but still a variant") + COUNTIF(F:F, "Not a variant: autograph transcript error") + COUNTIF(F:F, "Not a variant: apograph transcript error")</f>
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:AI1" xr:uid="{6186005F-94E2-41CC-8345-C084BDDA2E52}"/>
   <conditionalFormatting sqref="J2:J1048576">
-    <cfRule type="expression" dxfId="218" priority="54">
+    <cfRule type="expression" dxfId="232" priority="54">
       <formula>$J2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="217" priority="55">
+    <cfRule type="expression" dxfId="231" priority="55">
       <formula>$J2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:O1048576 R2:S1048576">
-    <cfRule type="expression" dxfId="216" priority="52">
+    <cfRule type="expression" dxfId="230" priority="52">
       <formula>AND(OR($J2="Addition",$J2="Omission"), K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="215" priority="53">
+    <cfRule type="expression" dxfId="229" priority="53">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:S1048576">
-    <cfRule type="expression" dxfId="214" priority="51">
+    <cfRule type="expression" dxfId="228" priority="51">
       <formula>AND(OR($J2="Addition",$J2="Omission"), K2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N1048576">
-    <cfRule type="expression" dxfId="213" priority="23">
+    <cfRule type="expression" dxfId="227" priority="23">
       <formula>AND($L2&lt;&gt;"",$L2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q1048576">
-    <cfRule type="expression" dxfId="212" priority="18">
+    <cfRule type="expression" dxfId="226" priority="18">
       <formula>$O2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="211" priority="19">
+    <cfRule type="expression" dxfId="225" priority="19">
       <formula>$O2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="21">
+    <cfRule type="expression" dxfId="224" priority="21">
       <formula>AND(OR($J2="Addition",$J2="Omission"), P2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="209" priority="22">
+    <cfRule type="expression" dxfId="223" priority="22">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R1048576">
-    <cfRule type="expression" dxfId="208" priority="41">
+    <cfRule type="expression" dxfId="222" priority="41">
       <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2 T3:V1048576">
-    <cfRule type="expression" dxfId="207" priority="47">
+    <cfRule type="expression" dxfId="221" priority="47">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="48">
+    <cfRule type="expression" dxfId="220" priority="48">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T3:V1048576 T2">
-    <cfRule type="expression" dxfId="205" priority="46">
+    <cfRule type="expression" dxfId="219" priority="46">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:V188">
-    <cfRule type="expression" dxfId="204" priority="1">
+    <cfRule type="expression" dxfId="218" priority="1">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="203" priority="2">
+    <cfRule type="expression" dxfId="217" priority="2">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="202" priority="3">
+    <cfRule type="expression" dxfId="216" priority="3">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W1048576">
-    <cfRule type="expression" dxfId="201" priority="7">
+    <cfRule type="expression" dxfId="215" priority="7">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="8">
+    <cfRule type="expression" dxfId="214" priority="8">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="199" priority="9">
+    <cfRule type="expression" dxfId="213" priority="9">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="13">
+    <cfRule type="expression" dxfId="212" priority="13">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="14">
+    <cfRule type="expression" dxfId="211" priority="14">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X1048576">
-    <cfRule type="expression" dxfId="196" priority="4">
+    <cfRule type="expression" dxfId="210" priority="4">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="195" priority="5">
+    <cfRule type="expression" dxfId="209" priority="5">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="194" priority="6">
+    <cfRule type="expression" dxfId="208" priority="6">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y1048576">
-    <cfRule type="expression" dxfId="193" priority="10">
+    <cfRule type="expression" dxfId="207" priority="10">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="192" priority="11">
+    <cfRule type="expression" dxfId="206" priority="11">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:AF1048576">
-    <cfRule type="expression" dxfId="191" priority="16">
+    <cfRule type="expression" dxfId="205" priority="16">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="190" priority="17">
+    <cfRule type="expression" dxfId="204" priority="17">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD1048576">
-    <cfRule type="expression" dxfId="189" priority="15">
+    <cfRule type="expression" dxfId="203" priority="15">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17455,43 +17756,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C4193BF0-4136-4BBC-B0AC-D2A0BF5246B4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0497AD02-B3E7-4282-BCBD-0B70C5B7A52D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7262AFA-8FBA-4F36-89B6-CE172EEB3CC4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A7DF72AC-78C4-40F1-BA39-594ED540D6C3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0D836A42-26EC-47D8-A184-246A8C35A40C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E9AFCED9-6A8C-4B7D-8F93-06161D78FE44}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5849044F-ACA6-458C-A05F-D60291614710}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF1048576</xm:sqref>
         </x14:dataValidation>
@@ -17503,7 +17804,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{89DB1C86-E161-46A3-A84F-ADF2A9324D19}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X1048576</xm:sqref>
         </x14:dataValidation>
@@ -17515,10 +17816,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DEF9D2-8DD6-40EE-A117-AEED6255AA6F}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -17544,34 +17845,37 @@
         <v>557</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>367</v>
       </c>
@@ -17597,31 +17901,34 @@
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>475</v>
+        <v>737</v>
       </c>
       <c r="J3" t="s">
+        <v>475</v>
+      </c>
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>506</v>
       </c>
-      <c r="L3" t="s">
-        <v>475</v>
-      </c>
       <c r="M3" t="s">
+        <v>475</v>
+      </c>
+      <c r="N3" t="s">
         <v>507</v>
       </c>
-      <c r="N3" t="s">
-        <v>475</v>
-      </c>
       <c r="O3" t="s">
+        <v>475</v>
+      </c>
+      <c r="P3" t="s">
         <v>508</v>
       </c>
-      <c r="P3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>338</v>
       </c>
@@ -17647,31 +17954,34 @@
         <v>559</v>
       </c>
       <c r="I4" t="s">
+        <v>738</v>
+      </c>
+      <c r="J4" t="s">
         <v>481</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>559</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>708</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>481</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>513</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>481</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>514</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>480</v>
       </c>
@@ -17690,17 +18000,20 @@
       <c r="F5" t="s">
         <v>549</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I5" t="s">
+        <v>739</v>
+      </c>
+      <c r="L5" t="s">
         <v>512</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>516</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>383</v>
       </c>
@@ -17713,14 +18026,14 @@
       <c r="E6" t="s">
         <v>518</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>519</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>484</v>
       </c>
@@ -17730,11 +18043,11 @@
       <c r="E7" t="s">
         <v>521</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>486</v>
       </c>
@@ -17744,11 +18057,11 @@
       <c r="E8" t="s">
         <v>523</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -17758,11 +18071,11 @@
       <c r="E9" t="s">
         <v>525</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>386</v>
       </c>
@@ -17772,44 +18085,44 @@
       <c r="E10" t="s">
         <v>527</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>472</v>
       </c>
       <c r="E11" t="s">
         <v>529</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>571</v>
       </c>
       <c r="E12" t="s">
         <v>567</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>488</v>
       </c>
       <c r="E13" t="s">
         <v>628</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>489</v>
       </c>
@@ -17817,12 +18130,12 @@
         <v>530</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>425</v>
       </c>
@@ -17855,7 +18168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2284323-354A-4331-A555-A32E76DD1723}">
-  <dimension ref="A1:AE68"/>
+  <dimension ref="A1:AE79"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -18239,7 +18552,9 @@
       <c r="S7" s="5">
         <v>1420</v>
       </c>
-      <c r="T7" s="5"/>
+      <c r="T7" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -21179,136 +21494,188 @@
         <v>481</v>
       </c>
     </row>
-    <row r="65" spans="18:19">
+    <row r="65" spans="18:30">
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
     </row>
-    <row r="66" spans="18:19">
+    <row r="66" spans="18:30">
       <c r="R66" s="5"/>
       <c r="S66" s="5"/>
     </row>
-    <row r="67" spans="18:19">
+    <row r="67" spans="18:30">
       <c r="R67" s="5"/>
       <c r="S67" s="5"/>
     </row>
-    <row r="68" spans="18:19">
+    <row r="68" spans="18:30">
       <c r="R68" s="5"/>
       <c r="S68" s="5"/>
     </row>
+    <row r="69" spans="18:30">
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+      <c r="AD69">
+        <f>COUNTIF(AD1:AD64, "Yes")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="18:30">
+      <c r="R70" s="5"/>
+      <c r="S70" s="5"/>
+      <c r="AD70">
+        <f>COUNTIF(AD1:AD64,"Yes")/COUNTA(AD1:AD64)</f>
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="71" spans="18:30">
+      <c r="R71" s="5"/>
+      <c r="S71" s="5"/>
+    </row>
+    <row r="72" spans="18:30">
+      <c r="R72" s="5"/>
+      <c r="S72" s="5"/>
+    </row>
+    <row r="73" spans="18:30">
+      <c r="R73" s="5"/>
+      <c r="S73" s="5"/>
+    </row>
+    <row r="74" spans="18:30">
+      <c r="R74" s="5"/>
+      <c r="S74" s="5"/>
+    </row>
+    <row r="75" spans="18:30">
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+    </row>
+    <row r="76" spans="18:30">
+      <c r="R76" s="5"/>
+      <c r="S76" s="5"/>
+    </row>
+    <row r="77" spans="18:30">
+      <c r="R77" s="5"/>
+      <c r="S77" s="5"/>
+    </row>
+    <row r="78" spans="18:30">
+      <c r="R78" s="5"/>
+      <c r="S78" s="5"/>
+    </row>
+    <row r="79" spans="18:30">
+      <c r="R79" s="5"/>
+      <c r="S79" s="5"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G64">
-    <cfRule type="expression" dxfId="188" priority="29">
+    <cfRule type="expression" dxfId="202" priority="29">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="187" priority="30">
+    <cfRule type="expression" dxfId="201" priority="30">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L64 O2:P64">
-    <cfRule type="expression" dxfId="186" priority="27">
+    <cfRule type="expression" dxfId="200" priority="27">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="28">
+    <cfRule type="expression" dxfId="199" priority="28">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P64">
-    <cfRule type="expression" dxfId="184" priority="26">
+    <cfRule type="expression" dxfId="198" priority="26">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K64">
-    <cfRule type="expression" dxfId="183" priority="21">
+    <cfRule type="expression" dxfId="197" priority="21">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N64">
-    <cfRule type="expression" dxfId="182" priority="17">
+    <cfRule type="expression" dxfId="196" priority="17">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="18">
+    <cfRule type="expression" dxfId="195" priority="18">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="19">
+    <cfRule type="expression" dxfId="194" priority="19">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="20">
+    <cfRule type="expression" dxfId="193" priority="20">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O64">
-    <cfRule type="expression" dxfId="178" priority="22">
+    <cfRule type="expression" dxfId="192" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AD2,6)&lt;&gt;"strict",$AC2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:S64 R2:S66">
-    <cfRule type="expression" dxfId="177" priority="23">
+    <cfRule type="expression" dxfId="191" priority="23">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="24">
+    <cfRule type="expression" dxfId="190" priority="24">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="25">
+    <cfRule type="expression" dxfId="189" priority="25">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R67:S68">
-    <cfRule type="expression" dxfId="174" priority="62">
+  <conditionalFormatting sqref="R67:S79">
+    <cfRule type="expression" dxfId="188" priority="62">
       <formula>AND(AND(LEFT(#REF!,3)="Sub", RIGHT(#REF!,4)&lt;&gt;"Form"),$S67&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="63">
+    <cfRule type="expression" dxfId="187" priority="63">
       <formula>AND(AND(LEFT(#REF!,3)="Sub", RIGHT(#REF!,4)&lt;&gt;"Form"),$S67="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="172" priority="64">
+    <cfRule type="expression" dxfId="186" priority="64">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T64">
-    <cfRule type="expression" dxfId="171" priority="7">
+    <cfRule type="expression" dxfId="185" priority="7">
       <formula>AND($V2&lt;&gt;"",OR($AC2="Yes",$AD2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="170" priority="8">
+    <cfRule type="expression" dxfId="184" priority="8">
       <formula>OR($AC2="Yes",$AD2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="9">
+    <cfRule type="expression" dxfId="183" priority="9">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="168" priority="12">
+    <cfRule type="expression" dxfId="182" priority="12">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="167" priority="13">
+    <cfRule type="expression" dxfId="181" priority="13">
       <formula>AND($AC2&lt;&gt;"Yes",$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U64">
-    <cfRule type="expression" dxfId="166" priority="4">
+    <cfRule type="expression" dxfId="180" priority="4">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$W2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="5">
+    <cfRule type="expression" dxfId="179" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="6">
+    <cfRule type="expression" dxfId="178" priority="6">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V64">
-    <cfRule type="expression" dxfId="163" priority="10">
+    <cfRule type="expression" dxfId="177" priority="10">
       <formula>AND($W2="Yes",$X2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="11">
+    <cfRule type="expression" dxfId="176" priority="11">
       <formula>$W2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:AC64">
-    <cfRule type="expression" dxfId="161" priority="15">
+    <cfRule type="expression" dxfId="175" priority="15">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="160" priority="16">
+    <cfRule type="expression" dxfId="174" priority="16">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA64">
-    <cfRule type="expression" dxfId="159" priority="14">
+    <cfRule type="expression" dxfId="173" priority="14">
       <formula>AND(OR($AA2&lt;&gt;"",$AB2&lt;&gt;""),$AC2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21367,43 +21734,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0E50FAC4-F329-4623-853C-18C025700CE3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{276E4FA1-D3C1-4253-9072-761C4EDE486A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{46EDC314-3E89-4913-8705-77FC6D7A961F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{30DA714A-2B3C-47E6-9813-FB2D3B88669D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8402065D-6E03-49FA-B3DC-6416612894EA}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B9B66BE-3D4E-4F93-9C21-46D2BBA9EB70}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EF1AD82C-1D37-46D0-892B-A6DA27CBCAA4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC64</xm:sqref>
         </x14:dataValidation>
@@ -21415,7 +21782,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{B0EA0A09-8484-4709-9000-AB0B894F657E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U64</xm:sqref>
         </x14:dataValidation>
@@ -21427,6 +21794,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C667950-7769-4646-B0BE-9F7BE30D02DF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF79"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
@@ -21522,7 +21890,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="29">
+    <row r="2" spans="1:31" ht="29" hidden="1">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -21583,7 +21951,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="29">
+    <row r="3" spans="1:31" ht="29" hidden="1">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -21705,7 +22073,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="29">
+    <row r="5" spans="1:31" ht="29" hidden="1">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -21766,7 +22134,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="43.5">
+    <row r="6" spans="1:31" ht="43.5" hidden="1">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -21830,7 +22198,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="43.5">
+    <row r="7" spans="1:31" ht="43.5" hidden="1">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -21892,7 +22260,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="174">
+    <row r="8" spans="1:31" ht="174" hidden="1">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -21953,7 +22321,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="43.5">
+    <row r="9" spans="1:31" ht="43.5" hidden="1">
       <c r="A9" t="s">
         <v>192</v>
       </c>
@@ -22016,7 +22384,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="116">
+    <row r="10" spans="1:31" ht="116" hidden="1">
       <c r="A10" t="s">
         <v>197</v>
       </c>
@@ -22077,7 +22445,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="43.5">
+    <row r="11" spans="1:31" ht="43.5" hidden="1">
       <c r="A11" t="s">
         <v>204</v>
       </c>
@@ -22139,7 +22507,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="72.5">
+    <row r="12" spans="1:31" ht="72.5" hidden="1">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -22203,7 +22571,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="72.5">
+    <row r="13" spans="1:31" ht="72.5" hidden="1">
       <c r="A13" t="s">
         <v>228</v>
       </c>
@@ -22264,7 +22632,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="43.5">
+    <row r="14" spans="1:31" ht="43.5" hidden="1">
       <c r="A14" t="s">
         <v>237</v>
       </c>
@@ -22323,7 +22691,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="29">
+    <row r="15" spans="1:31" ht="29" hidden="1">
       <c r="A15" t="s">
         <v>241</v>
       </c>
@@ -22384,7 +22752,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="29">
+    <row r="16" spans="1:31" ht="29" hidden="1">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -22443,7 +22811,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="116">
+    <row r="17" spans="1:32" ht="116" hidden="1">
       <c r="A17" t="s">
         <v>259</v>
       </c>
@@ -22507,7 +22875,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="29">
+    <row r="18" spans="1:32" ht="29" hidden="1">
       <c r="A18" t="s">
         <v>260</v>
       </c>
@@ -22566,7 +22934,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="72.5">
+    <row r="19" spans="1:32" ht="72.5" hidden="1">
       <c r="A19" t="s">
         <v>280</v>
       </c>
@@ -22693,7 +23061,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="101.5">
+    <row r="21" spans="1:32" ht="101.5" hidden="1">
       <c r="A21" t="s">
         <v>314</v>
       </c>
@@ -22759,7 +23127,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="43.5">
+    <row r="22" spans="1:32" ht="43.5" hidden="1">
       <c r="A22" t="s">
         <v>325</v>
       </c>
@@ -22822,7 +23190,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="29">
+    <row r="23" spans="1:32" ht="29" hidden="1">
       <c r="A23" t="s">
         <v>325</v>
       </c>
@@ -22885,7 +23253,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="72.5">
+    <row r="24" spans="1:32" ht="72.5" hidden="1">
       <c r="A24" t="s">
         <v>326</v>
       </c>
@@ -22953,7 +23321,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="43.5">
+    <row r="25" spans="1:32" ht="43.5" hidden="1">
       <c r="A25" t="s">
         <v>331</v>
       </c>
@@ -23644,133 +24012,153 @@
       <c r="T79" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AF25" xr:uid="{5C667950-7769-4646-B0BE-9F7BE30D02DF}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Omission"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="3"/>
+        <filter val="4"/>
+        <filter val="5"/>
+        <filter val="7"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="30">
+      <filters>
+        <filter val="Yes"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="D44:F44"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:G25">
-    <cfRule type="expression" dxfId="158" priority="32">
+    <cfRule type="expression" dxfId="172" priority="33">
+      <formula>$I2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="171" priority="32">
       <formula>$I2&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="157" priority="33">
-      <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L25 O2:P25">
-    <cfRule type="expression" dxfId="156" priority="30">
+    <cfRule type="expression" dxfId="170" priority="31">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="169" priority="30">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="155" priority="31">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P25">
-    <cfRule type="expression" dxfId="154" priority="29">
+    <cfRule type="expression" dxfId="168" priority="29">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K25">
-    <cfRule type="expression" dxfId="153" priority="24">
+    <cfRule type="expression" dxfId="167" priority="24">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N25">
-    <cfRule type="expression" dxfId="152" priority="20">
-      <formula>$N2="Absent"</formula>
+    <cfRule type="expression" dxfId="166" priority="23">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="21">
+    <cfRule type="expression" dxfId="165" priority="22">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="164" priority="21">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="22">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="149" priority="23">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
+    <cfRule type="expression" dxfId="163" priority="20">
+      <formula>$N2="Absent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O25">
-    <cfRule type="expression" dxfId="148" priority="25">
+    <cfRule type="expression" dxfId="162" priority="25">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q25">
-    <cfRule type="expression" dxfId="147" priority="1">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="2">
+    <cfRule type="expression" dxfId="161" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="3">
+    <cfRule type="expression" dxfId="160" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="159" priority="1">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T25">
-    <cfRule type="expression" dxfId="144" priority="26">
+    <cfRule type="expression" dxfId="158" priority="26">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="143" priority="27">
+    <cfRule type="expression" dxfId="157" priority="27">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="28">
+    <cfRule type="expression" dxfId="156" priority="28">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T79">
-    <cfRule type="expression" dxfId="141" priority="4">
+    <cfRule type="expression" dxfId="155" priority="4">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="5">
+    <cfRule type="expression" dxfId="154" priority="5">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="6">
+    <cfRule type="expression" dxfId="153" priority="6">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U25">
-    <cfRule type="expression" dxfId="138" priority="10">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+    <cfRule type="expression" dxfId="152" priority="16">
+      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="11">
+    <cfRule type="expression" dxfId="151" priority="15">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="150" priority="12">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="149" priority="11">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="12">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="135" priority="15">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="16">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="148" priority="10">
+      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V25">
-    <cfRule type="expression" dxfId="133" priority="7">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+    <cfRule type="expression" dxfId="147" priority="9">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="8">
+    <cfRule type="expression" dxfId="146" priority="8">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="131" priority="9">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    <cfRule type="expression" dxfId="145" priority="7">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W25">
-    <cfRule type="expression" dxfId="130" priority="13">
+    <cfRule type="expression" dxfId="144" priority="14">
+      <formula>$X2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="143" priority="13">
       <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="129" priority="14">
-      <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AD25">
-    <cfRule type="expression" dxfId="128" priority="18">
+    <cfRule type="expression" dxfId="142" priority="18">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="19">
+    <cfRule type="expression" dxfId="141" priority="19">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB25">
-    <cfRule type="expression" dxfId="126" priority="17">
+    <cfRule type="expression" dxfId="140" priority="17">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23829,43 +24217,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8CA3A396-2805-4983-953E-07A7A0F0F542}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{04F9B335-6338-467A-9F10-1D779666532C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{98B197D6-BFAC-46C2-AA0A-F0DA633CEDED}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0C8B847-9553-46F8-8093-0B35DB33EA84}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C93C5276-468D-4082-96FA-3F97AFA94845}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D8AB39A9-142A-42DB-AB8A-98E8E92E016D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9233A31E-FC6C-4930-8D7A-5ED209F48CE5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD25</xm:sqref>
         </x14:dataValidation>
@@ -23877,7 +24265,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{0DA40CB8-C07E-43E1-80D4-827D91088F0C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V25</xm:sqref>
         </x14:dataValidation>
@@ -24810,129 +25198,129 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G13">
-    <cfRule type="expression" dxfId="125" priority="32">
+    <cfRule type="expression" dxfId="139" priority="33">
+      <formula>$I2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="138" priority="32">
       <formula>$I2&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="33">
-      <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L13 O2:P13">
-    <cfRule type="expression" dxfId="123" priority="30">
+    <cfRule type="expression" dxfId="137" priority="31">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="136" priority="30">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="122" priority="31">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P13">
-    <cfRule type="expression" dxfId="121" priority="29">
+    <cfRule type="expression" dxfId="135" priority="29">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K13">
-    <cfRule type="expression" dxfId="120" priority="24">
+    <cfRule type="expression" dxfId="134" priority="24">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N13">
-    <cfRule type="expression" dxfId="119" priority="20">
-      <formula>$N2="Absent"</formula>
+    <cfRule type="expression" dxfId="133" priority="23">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="21">
+    <cfRule type="expression" dxfId="132" priority="22">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="131" priority="21">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="22">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="116" priority="23">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
+    <cfRule type="expression" dxfId="130" priority="20">
+      <formula>$N2="Absent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O13">
-    <cfRule type="expression" dxfId="115" priority="25">
+    <cfRule type="expression" dxfId="129" priority="25">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q13">
-    <cfRule type="expression" dxfId="114" priority="1">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="113" priority="2">
+    <cfRule type="expression" dxfId="128" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="3">
+    <cfRule type="expression" dxfId="127" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="126" priority="1">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T13">
-    <cfRule type="expression" dxfId="111" priority="26">
+    <cfRule type="expression" dxfId="125" priority="26">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="27">
+    <cfRule type="expression" dxfId="124" priority="27">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="28">
+    <cfRule type="expression" dxfId="123" priority="28">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T13">
-    <cfRule type="expression" dxfId="108" priority="4">
+    <cfRule type="expression" dxfId="122" priority="4">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="5">
+    <cfRule type="expression" dxfId="121" priority="5">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="6">
+    <cfRule type="expression" dxfId="120" priority="6">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U13">
-    <cfRule type="expression" dxfId="105" priority="10">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+    <cfRule type="expression" dxfId="119" priority="16">
+      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="11">
+    <cfRule type="expression" dxfId="118" priority="15">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="117" priority="12">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="116" priority="11">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="12">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="15">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="16">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="115" priority="10">
+      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V13">
-    <cfRule type="expression" dxfId="100" priority="7">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+    <cfRule type="expression" dxfId="114" priority="9">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="8">
+    <cfRule type="expression" dxfId="113" priority="8">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="9">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    <cfRule type="expression" dxfId="112" priority="7">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W13">
-    <cfRule type="expression" dxfId="97" priority="13">
+    <cfRule type="expression" dxfId="111" priority="14">
+      <formula>$X2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="13">
       <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="14">
-      <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AD13">
-    <cfRule type="expression" dxfId="95" priority="18">
+    <cfRule type="expression" dxfId="109" priority="18">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="19">
+    <cfRule type="expression" dxfId="108" priority="19">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB13">
-    <cfRule type="expression" dxfId="93" priority="17">
+    <cfRule type="expression" dxfId="107" priority="17">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24949,7 +25337,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{BA005DD2-2201-45EB-B2D0-B082B138AA29}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V13</xm:sqref>
         </x14:dataValidation>
@@ -24961,43 +25349,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C9C8470B-A00B-4409-B059-55160C8C6A64}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EDB16C1-D16C-453B-ABF1-025859FE6BB9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FD29CCB0-373F-43C9-8170-F48E496C5BF0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{73FD491A-8FB1-431A-8994-67D12FC978FB}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ADFE6369-5B67-4599-977A-28B349A2D4A4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44E63D03-7ACF-46D7-A095-04DDFC4D9C84}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{42CFE370-997E-40DF-B0E5-016879F249A4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W13</xm:sqref>
         </x14:dataValidation>
@@ -25355,129 +25743,129 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="expression" dxfId="92" priority="32">
+    <cfRule type="expression" dxfId="106" priority="33">
+      <formula>$I2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="105" priority="32">
       <formula>$I2&lt;&gt;""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="91" priority="33">
-      <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L3 O2:P3">
-    <cfRule type="expression" dxfId="90" priority="30">
+    <cfRule type="expression" dxfId="104" priority="31">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="103" priority="30">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="89" priority="31">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P3">
-    <cfRule type="expression" dxfId="88" priority="29">
+    <cfRule type="expression" dxfId="102" priority="29">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
-    <cfRule type="expression" dxfId="87" priority="24">
+    <cfRule type="expression" dxfId="101" priority="24">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N3">
-    <cfRule type="expression" dxfId="86" priority="20">
-      <formula>$N2="Absent"</formula>
+    <cfRule type="expression" dxfId="100" priority="23">
+      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="21">
+    <cfRule type="expression" dxfId="99" priority="22">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="21">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="22">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="23">
-      <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
+    <cfRule type="expression" dxfId="97" priority="20">
+      <formula>$N2="Absent"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O3">
-    <cfRule type="expression" dxfId="82" priority="25">
+    <cfRule type="expression" dxfId="96" priority="25">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q3">
-    <cfRule type="expression" dxfId="81" priority="1">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="2">
+    <cfRule type="expression" dxfId="95" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="3">
+    <cfRule type="expression" dxfId="94" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="93" priority="1">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T3">
-    <cfRule type="expression" dxfId="78" priority="26">
+    <cfRule type="expression" dxfId="92" priority="26">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="27">
+    <cfRule type="expression" dxfId="91" priority="27">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="28">
+    <cfRule type="expression" dxfId="90" priority="28">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T3">
-    <cfRule type="expression" dxfId="75" priority="4">
+    <cfRule type="expression" dxfId="89" priority="4">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="5">
+    <cfRule type="expression" dxfId="88" priority="5">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="6">
+    <cfRule type="expression" dxfId="87" priority="6">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U3">
-    <cfRule type="expression" dxfId="72" priority="10">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+    <cfRule type="expression" dxfId="86" priority="16">
+      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="11">
+    <cfRule type="expression" dxfId="85" priority="15">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="12">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="11">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="12">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="15">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="16">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="82" priority="10">
+      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V3">
-    <cfRule type="expression" dxfId="67" priority="7">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+    <cfRule type="expression" dxfId="81" priority="9">
+      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="8">
+    <cfRule type="expression" dxfId="80" priority="8">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="9">
-      <formula>OR($I2="",$I2="Unclear due to correction")</formula>
+    <cfRule type="expression" dxfId="79" priority="7">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W3">
-    <cfRule type="expression" dxfId="64" priority="13">
+    <cfRule type="expression" dxfId="78" priority="14">
+      <formula>$X2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="13">
       <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="14">
-      <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AD3">
-    <cfRule type="expression" dxfId="62" priority="18">
+    <cfRule type="expression" dxfId="76" priority="18">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="19">
+    <cfRule type="expression" dxfId="75" priority="19">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB3">
-    <cfRule type="expression" dxfId="60" priority="17">
+    <cfRule type="expression" dxfId="74" priority="17">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25493,7 +25881,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{BEB85DE5-36FA-4A5E-A1FD-4EC0E4BD7D77}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V3</xm:sqref>
         </x14:dataValidation>
@@ -25505,43 +25893,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E4CB0715-561B-44BC-9A0B-13089FB83404}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{57FF3631-9ECE-40D8-A4E0-26CADEC9AD77}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB5F3466-80C2-4F6A-8AA5-0C569A148EE0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F776C2A-EA67-46D1-BB12-B942B3C02D6A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80B1F92E-6F06-4A65-9149-B93061FFED63}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EE3D3E36-4E91-48E1-83F0-A6F05626B816}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5C0637A6-F3A2-44FE-8EE6-4D3A2131FBB6}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W3</xm:sqref>
         </x14:dataValidation>
@@ -26632,118 +27020,118 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="expression" dxfId="59" priority="32">
+    <cfRule type="expression" dxfId="73" priority="32">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="33">
+    <cfRule type="expression" dxfId="72" priority="33">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L15 O2:P15">
-    <cfRule type="expression" dxfId="57" priority="30">
+    <cfRule type="expression" dxfId="71" priority="30">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="31">
+    <cfRule type="expression" dxfId="70" priority="31">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P15">
-    <cfRule type="expression" dxfId="55" priority="29">
+    <cfRule type="expression" dxfId="69" priority="29">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="expression" dxfId="54" priority="24">
+    <cfRule type="expression" dxfId="68" priority="24">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N15">
-    <cfRule type="expression" dxfId="53" priority="20">
+    <cfRule type="expression" dxfId="67" priority="20">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="21">
+    <cfRule type="expression" dxfId="66" priority="21">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="22">
+    <cfRule type="expression" dxfId="65" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="23">
+    <cfRule type="expression" dxfId="64" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O15">
-    <cfRule type="expression" dxfId="49" priority="25">
+    <cfRule type="expression" dxfId="63" priority="25">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AG2,6)&lt;&gt;"strict",$AF2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:S15">
-    <cfRule type="expression" dxfId="48" priority="26">
+    <cfRule type="expression" dxfId="62" priority="26">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="27">
+    <cfRule type="expression" dxfId="61" priority="27">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="28">
+    <cfRule type="expression" dxfId="60" priority="28">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:V15">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="2">
+    <cfRule type="expression" dxfId="58" priority="2">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="expression" dxfId="42" priority="10">
+    <cfRule type="expression" dxfId="56" priority="10">
       <formula>AND($Y2&lt;&gt;"",OR($AF2="Yes",$AG2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="11">
+    <cfRule type="expression" dxfId="55" priority="11">
       <formula>OR($AF2="Yes",$AG2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="12">
+    <cfRule type="expression" dxfId="54" priority="12">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="15">
+    <cfRule type="expression" dxfId="53" priority="15">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="16">
+    <cfRule type="expression" dxfId="52" priority="16">
       <formula>AND($AF2&lt;&gt;"Yes",$AG2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="expression" dxfId="37" priority="7">
+    <cfRule type="expression" dxfId="51" priority="7">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$Z2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="8">
+    <cfRule type="expression" dxfId="50" priority="8">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="9">
+    <cfRule type="expression" dxfId="49" priority="9">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="expression" dxfId="34" priority="13">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>AND($Z2="Yes",$AA2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="14">
+    <cfRule type="expression" dxfId="47" priority="14">
       <formula>$Z2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:AF15">
-    <cfRule type="expression" dxfId="32" priority="18">
+    <cfRule type="expression" dxfId="46" priority="18">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="19">
+    <cfRule type="expression" dxfId="45" priority="19">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="expression" dxfId="30" priority="17">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>AND(OR($AD2&lt;&gt;"",$AE2&lt;&gt;""),$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26802,43 +27190,43 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{03BC9159-3475-42FA-801F-1F413D0C6162}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5AE88BE0-EB5C-4CD3-9CD8-1DBFC1567DE2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F060AAD-17CE-4AD2-9EC3-3345E3CFF2F8}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{08D6BA09-0F5B-4C1F-ABE3-D1481E499FD7}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{384C6567-E5C3-4B65-87DB-791DF8AF623E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9FE69611-E110-4C5D-A22A-4646BBBAA1C9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{07048DFC-5092-4ADE-8DE3-74C51B54B726}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF15</xm:sqref>
         </x14:dataValidation>
@@ -26850,7 +27238,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{D24AFA59-5595-4946-8D01-2B3E792304B1}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X15</xm:sqref>
         </x14:dataValidation>
@@ -26862,10 +27250,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0A7D06-E459-49AE-87EA-7CDF8EA56F7F}">
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AG30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="1" customFormat="1" ht="29">
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -26927,37 +27318,40 @@
         <v>557</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="29">
+    <row r="2" spans="1:33" ht="29">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -27002,22 +27396,25 @@
       <c r="U2" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V2" s="5"/>
+      <c r="V2" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
-      <c r="Y2" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="29">
+      <c r="AE2" s="5"/>
+      <c r="AF2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="29">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -27062,36 +27459,39 @@
       <c r="U3" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V3" s="5"/>
+      <c r="V3" s="5" t="s">
+        <v>737</v>
+      </c>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
-      <c r="Y3" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
-      <c r="AE3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
+      <c r="AE3" s="5"/>
+      <c r="AF3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="29">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>554</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>555</v>
       </c>
       <c r="G4" t="s">
-        <v>615</v>
+        <v>745</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
@@ -27102,34 +27502,42 @@
       <c r="O4" s="7"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>604</v>
+      <c r="R4" s="5">
+        <f>1420-1204</f>
+        <v>216</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" ref="S4" ca="1" si="0">IF(ISNUMBER(R4),VALUE(MID(_xlfn.FORMULATEXT(R4),SEARCH("-",_xlfn.FORMULATEXT(R4))+1,LEN(_xlfn.FORMULATEXT(R4))-SEARCH("-",_xlfn.FORMULATEXT(R4)))), "")</f>
+        <v>1204</v>
+      </c>
+      <c r="T4" s="5">
+        <f t="shared" ref="T4" ca="1" si="1">IF(ISNUMBER(R4), VALUE(MID(_xlfn.FORMULATEXT(R4), 2, SEARCH("-", _xlfn.FORMULATEXT(R4)) - 2)), "")</f>
+        <v>1420</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="V4" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
-      <c r="Y4" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
-      <c r="AE4" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32">
+      <c r="AE4" s="5"/>
+      <c r="AF4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>107</v>
@@ -27138,7 +27546,7 @@
         <v>108</v>
       </c>
       <c r="G5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>546</v>
@@ -27162,33 +27570,36 @@
       <c r="U5" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V5" s="5"/>
+      <c r="V5" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
-      <c r="Y5" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
-      <c r="AE5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="29">
+      <c r="AE5" s="5"/>
+      <c r="AF5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="G6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>546</v>
@@ -27212,59 +27623,49 @@
       <c r="U6" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V6" s="5"/>
+      <c r="V6" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
-      <c r="Y6" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
-      <c r="AE6" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="43.5">
+      <c r="AE6" s="5"/>
+      <c r="AF6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="29">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>374</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="F7" t="s">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="G7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>479</v>
+        <v>546</v>
       </c>
       <c r="I7" s="5"/>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5">
-        <v>3</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>510</v>
-      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="7"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5">
-        <v>19277</v>
-      </c>
+      <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
         <v>604</v>
@@ -27275,46 +27676,62 @@
       <c r="U7" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V7" s="5"/>
+      <c r="V7" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
-      <c r="Y7" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
-      <c r="AE7" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="29">
+      <c r="AE7" s="5"/>
+      <c r="AF7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="43.5">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>393</v>
+        <v>375</v>
+      </c>
+      <c r="F8" t="s">
+        <v>337</v>
       </c>
       <c r="G8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>546</v>
+        <v>479</v>
       </c>
       <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>3</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>510</v>
+      </c>
       <c r="N8" s="5"/>
       <c r="O8" s="7"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>19277</v>
+      </c>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
         <v>604</v>
@@ -27325,56 +27742,49 @@
       <c r="U8" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V8" s="5"/>
+      <c r="V8" s="5" t="s">
+        <v>737</v>
+      </c>
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
-      <c r="Y8" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
-      <c r="AE8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="29">
+      <c r="AE8" s="5"/>
+      <c r="AF8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="29">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="G9" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>479</v>
+        <v>546</v>
       </c>
       <c r="I9" s="5"/>
-      <c r="J9" s="5">
-        <v>1</v>
-      </c>
-      <c r="K9" s="5">
-        <v>1</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>549</v>
-      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="7"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="5">
-        <v>19277</v>
-      </c>
+      <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5" t="s">
         <v>604</v>
@@ -27385,150 +27795,154 @@
       <c r="U9" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V9" s="5"/>
+      <c r="V9" s="5" t="s">
+        <v>737</v>
+      </c>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
-      <c r="Y9" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA9" s="5"/>
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
-      <c r="AE9" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32">
+      <c r="AE9" s="5"/>
+      <c r="AF9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="29">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>600</v>
+        <v>428</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>599</v>
+        <v>429</v>
       </c>
       <c r="G10" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>549</v>
+      </c>
       <c r="N10" s="5"/>
       <c r="O10" s="7"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5">
-        <v>-198</v>
-      </c>
-      <c r="S10" s="5">
-        <v>240</v>
-      </c>
-      <c r="T10" s="5">
-        <v>42</v>
+      <c r="Q10" s="5">
+        <v>19277</v>
+      </c>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>604</v>
       </c>
       <c r="U10" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V10" s="5"/>
+      <c r="V10" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
-      <c r="Y10" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA10" s="5"/>
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
-      <c r="AE10" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="130.5">
+      <c r="AE10" s="5"/>
+      <c r="AF10" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>451</v>
+        <v>599</v>
       </c>
       <c r="G11" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>479</v>
+        <v>545</v>
       </c>
       <c r="I11" s="5"/>
-      <c r="J11" s="5">
-        <v>4</v>
-      </c>
-      <c r="K11" s="5">
-        <v>17</v>
-      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
       <c r="L11" s="5"/>
-      <c r="M11" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>601</v>
-      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="7"/>
       <c r="P11" s="5"/>
-      <c r="Q11" s="5">
-        <v>43</v>
-      </c>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>604</v>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5">
+        <v>-198</v>
+      </c>
+      <c r="S11" s="5">
+        <v>240</v>
+      </c>
+      <c r="T11" s="5">
+        <v>42</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V11" s="5"/>
+      <c r="V11" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
-      <c r="Y11" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA11" s="5"/>
       <c r="AB11" s="5"/>
       <c r="AC11" s="5"/>
       <c r="AD11" s="5"/>
-      <c r="AE11" t="s">
-        <v>475</v>
-      </c>
+      <c r="AE11" s="5"/>
       <c r="AF11" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="101.5">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="130.5">
       <c r="A12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>479</v>
@@ -27538,17 +27952,17 @@
         <v>4</v>
       </c>
       <c r="K12" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
         <v>504</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5">
@@ -27564,58 +27978,63 @@
       <c r="U12" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V12" s="5"/>
+      <c r="V12" s="5" t="s">
+        <v>738</v>
+      </c>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
-      <c r="Y12" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA12" s="5"/>
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
-      <c r="AE12" t="s">
-        <v>481</v>
-      </c>
+      <c r="AE12" s="5"/>
       <c r="AF12" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="43.5">
+        <v>475</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="101.5">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G13" t="s">
-        <v>729</v>
+        <v>627</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>479</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K13" s="5">
-        <v>2</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>509</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="N13" s="5"/>
-      <c r="O13" s="7"/>
+        <v>504</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>602</v>
+      </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5">
-        <v>19277</v>
+        <v>43</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5" t="s">
@@ -27627,59 +28046,61 @@
       <c r="U13" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V13" s="5"/>
+      <c r="V13" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
-      <c r="Y13" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA13" s="5"/>
       <c r="AB13" s="5"/>
       <c r="AC13" s="5"/>
-      <c r="AD13" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="29">
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" t="s">
+        <v>481</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="43.5">
       <c r="A14" t="s">
         <v>325</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G14" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <v>1</v>
       </c>
       <c r="K14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>549</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="5" t="s">
-        <v>505</v>
-      </c>
+      <c r="P14" s="5"/>
       <c r="Q14" s="5">
-        <v>370</v>
+        <v>19277</v>
       </c>
       <c r="R14" s="5"/>
       <c r="S14" s="5" t="s">
@@ -27691,178 +28112,184 @@
       <c r="U14" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V14" s="5"/>
+      <c r="V14" s="5" t="s">
+        <v>737</v>
+      </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
-      <c r="Y14" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
-      <c r="AE14" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="29">
+      <c r="AE14" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="29">
       <c r="A15" t="s">
         <v>325</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G15" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>545</v>
+        <v>476</v>
       </c>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>549</v>
+      </c>
       <c r="N15" s="5"/>
       <c r="O15" s="7"/>
       <c r="P15" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5">
-        <v>30</v>
-      </c>
-      <c r="S15" s="5">
-        <v>47</v>
-      </c>
-      <c r="T15" s="5">
-        <v>77</v>
+        <v>505</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>370</v>
+      </c>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>604</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V15" s="5"/>
+      <c r="V15" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
-      <c r="Y15" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA15" s="5"/>
       <c r="AB15" s="5"/>
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
-      <c r="AE15" t="s">
+      <c r="AE15" s="5"/>
+      <c r="AF15" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="72.5">
+    <row r="16" spans="1:33" ht="29">
       <c r="A16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G16" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>479</v>
+        <v>545</v>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="5">
-        <v>3</v>
-      </c>
-      <c r="K16" s="5">
-        <v>14</v>
-      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5">
-        <v>119</v>
-      </c>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="T16" s="5" t="s">
-        <v>604</v>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5">
+        <v>30</v>
+      </c>
+      <c r="S16" s="5">
+        <v>47</v>
+      </c>
+      <c r="T16" s="5">
+        <v>77</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V16" s="5"/>
+      <c r="V16" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
-      <c r="Y16" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
       <c r="AC16" s="5"/>
-      <c r="AD16" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="AE16" t="s">
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" t="s">
         <v>481</v>
       </c>
-      <c r="AF16" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="43.5">
+    </row>
+    <row r="17" spans="1:33" ht="72.5">
       <c r="A17" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G17" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>479</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" s="5">
-        <v>2</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>509</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="N17" s="5"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="5" t="s">
-        <v>511</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="P17" s="5"/>
       <c r="Q17" s="5">
-        <v>19277</v>
+        <v>119</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5" t="s">
@@ -27874,167 +28301,410 @@
       <c r="U17" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V17" s="5"/>
+      <c r="V17" s="5" t="s">
+        <v>739</v>
+      </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
-      <c r="Y17" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="Z17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5" t="s">
+        <v>475</v>
+      </c>
       <c r="AA17" s="5"/>
       <c r="AB17" s="5"/>
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
-      <c r="AE17" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31">
-      <c r="D20" t="s">
+      <c r="AE17" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>481</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" ht="43.5">
+      <c r="A18" t="s">
+        <v>331</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="G18" t="s">
+        <v>735</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>19277</v>
+      </c>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="V18" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
+      <c r="D21" t="s">
         <v>700</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <f>COUNTIF(U:U, "Harmonizing")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31">
-      <c r="D21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
+      <c r="D22" t="s">
         <v>701</v>
       </c>
-      <c r="E21">
+      <c r="E22">
         <f>COUNTIF(U:U, "Disharmonizing")</f>
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
-      <c r="D22" t="s">
+    <row r="23" spans="1:33">
+      <c r="D23" t="s">
         <v>702</v>
       </c>
-      <c r="E22">
-        <f>E20/(E20+E21)</f>
+      <c r="E23">
+        <f>E21/(E21+E22)</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
+      <c r="E26" s="15" t="s">
+        <v>740</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:33">
+      <c r="E27" t="s">
+        <v>741</v>
+      </c>
+      <c r="F27" t="s">
+        <v>742</v>
+      </c>
+      <c r="G27" t="s">
+        <v>743</v>
+      </c>
+      <c r="H27" t="s">
+        <v>744</v>
+      </c>
+      <c r="I27" t="s">
+        <v>739</v>
+      </c>
+      <c r="J27" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
+      <c r="D28" t="s">
+        <v>700</v>
+      </c>
+      <c r="E28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward")</f>
         <v>0</v>
       </c>
+      <c r="F28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward")</f>
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
+      <c r="D29" t="s">
+        <v>701</v>
+      </c>
+      <c r="E29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward")</f>
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward")</f>
+        <v>5</v>
+      </c>
+      <c r="H29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>12</v>
+      </c>
+      <c r="I29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>7</v>
+      </c>
+      <c r="J29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
+      <c r="D30" t="s">
+        <v>702</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="E30:G30" si="2">E28/(E28+E29)</f>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H30">
+        <f t="shared" ref="H30:J30" si="3">H28/(H28+H29)</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H17">
-    <cfRule type="expression" dxfId="29" priority="29">
+  <mergeCells count="1">
+    <mergeCell ref="E26:H26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H2:H18">
+    <cfRule type="expression" dxfId="43" priority="34">
       <formula>$J2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="42" priority="35">
       <formula>$J2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:M17 P2:Q17">
-    <cfRule type="expression" dxfId="27" priority="27">
+  <conditionalFormatting sqref="I2:M18 P4:Q4">
+    <cfRule type="expression" dxfId="41" priority="32">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="40" priority="33">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:Q17">
-    <cfRule type="expression" dxfId="25" priority="26">
+  <conditionalFormatting sqref="I2:Q18">
+    <cfRule type="expression" dxfId="39" priority="31">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L17">
-    <cfRule type="expression" dxfId="24" priority="21">
+  <conditionalFormatting sqref="L2:L18">
+    <cfRule type="expression" dxfId="38" priority="26">
       <formula>AND($L2&lt;&gt;"",$L2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O17">
-    <cfRule type="expression" dxfId="23" priority="17">
+  <conditionalFormatting sqref="N2:O18">
+    <cfRule type="expression" dxfId="37" priority="23">
+      <formula>$O2="NA"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="22">
       <formula>$O2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
-      <formula>$O2="NA"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="35" priority="24">
       <formula>AND(OR($J2="Addition",$J2="Omission"), N2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="34" priority="25">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P17">
-    <cfRule type="expression" dxfId="19" priority="22">
-      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
+  <conditionalFormatting sqref="P2:P18">
+    <cfRule type="expression" dxfId="33" priority="57">
+      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AF2,6)&lt;&gt;"strict",$AE2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:T17">
-    <cfRule type="expression" dxfId="18" priority="23">
+  <conditionalFormatting sqref="P2:Q3 P5:Q18">
+    <cfRule type="expression" dxfId="32" priority="63">
+      <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="62">
+      <formula>AND(OR($J2="Addition",$J2="Omission"), P2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:T18">
+    <cfRule type="expression" dxfId="30" priority="28">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="24">
+    <cfRule type="expression" dxfId="29" priority="29">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="25">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:T17">
-    <cfRule type="expression" dxfId="15" priority="1">
+  <conditionalFormatting sqref="S2:T18">
+    <cfRule type="expression" dxfId="27" priority="6">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="26" priority="7">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="25" priority="8">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U17">
-    <cfRule type="expression" dxfId="12" priority="7">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+  <conditionalFormatting sqref="U4">
+    <cfRule type="expression" dxfId="24" priority="73">
+      <formula>AND($J4&lt;&gt;"",$J4&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
-      <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
+    <cfRule type="expression" dxfId="23" priority="71">
+      <formula>AND($W4&lt;&gt;"",OR($AE4="Yes",$AF4&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="22" priority="72">
+      <formula>OR($AE4="Yes",$AF4&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="74">
+      <formula>OR($J4="",$J4="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="75">
+      <formula>AND($AE4&lt;&gt;"Yes",$AF4="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:V3 U5:V18">
+    <cfRule type="expression" dxfId="19" priority="43">
+      <formula>OR($AE2="Yes",$AF2&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="47">
+      <formula>OR($J2="",$J2="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="48">
+      <formula>AND($AE2&lt;&gt;"Yes",$AF2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="44">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="15" priority="42">
+      <formula>AND($X2&lt;&gt;"",OR($AE2="Yes",$AF2&lt;&gt;""))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V4">
+    <cfRule type="expression" dxfId="14" priority="1">
+      <formula>AND($X4&lt;&gt;"",OR($AE4="Yes",$AF4&lt;&gt;""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND($AE4&lt;&gt;"Yes",$AF4="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>OR($J4="",$J4="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>AND($J4&lt;&gt;"",$J4&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>OR($AE4="Yes",$AF4&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W3 W5:W18">
+    <cfRule type="expression" dxfId="9" priority="40">
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="41">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="13">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="7" priority="39">
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V17">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+  <conditionalFormatting sqref="W4">
+    <cfRule type="expression" dxfId="6" priority="77">
+      <formula>$X4=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
+    <cfRule type="expression" dxfId="5" priority="76">
+      <formula>AND($X4="Yes",$Z4="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X3 X5:X18">
+    <cfRule type="expression" dxfId="4" priority="46">
+      <formula>$Y2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="45">
+      <formula>AND($Y2="Yes",$Z2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:AE3 W4:AE4 X5:AE18">
+    <cfRule type="expression" dxfId="2" priority="51">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W17">
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="11">
-      <formula>$X2=""</formula>
+  <conditionalFormatting sqref="X2:AE3 X5:AE18 W4:AE4">
+    <cfRule type="expression" dxfId="1" priority="50">
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:AD17">
-    <cfRule type="expression" dxfId="2" priority="15">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="16">
-      <formula>OR($J2="",$J2="Unclear due to correction")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB17">
-    <cfRule type="expression" dxfId="0" priority="14">
-      <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
+  <conditionalFormatting sqref="AC2:AC18">
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>AND(OR($AC2&lt;&gt;"",$AD2&lt;&gt;""),$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE17" xr:uid="{92A51B07-67FE-4A0E-A375-07B4D97B4627}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG4 AF2:AF18" xr:uid="{92A51B07-67FE-4A0E-A375-07B4D97B4627}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -28043,102 +28713,108 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="17">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5FB75010-4FCA-4320-AD4C-7F042FD4D6EB}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H17</xm:sqref>
+          <xm:sqref>H2:H18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B8E581F1-394C-4A91-A36C-9A5B4DE66276}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$C$2:$C$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F17</xm:sqref>
+          <xm:sqref>F2:F18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{5B123D06-C1C0-4BE5-B7A2-F08BA152565A}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D17</xm:sqref>
+          <xm:sqref>D2:D18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Just pick &quot;yes&quot; or &quot;no&quot;!!!" xr:uid="{32F550F3-778F-44E4-AED0-AB136BB8E9D3}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E17</xm:sqref>
+          <xm:sqref>E2:E18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9B352F0-EE44-47A8-92D6-66EFA984A522}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$E$2:$E$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L17</xm:sqref>
+          <xm:sqref>L2:L18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8CEB19C7-D189-44BB-BB60-D7E64485472A}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$F$2:$F$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M17</xm:sqref>
+          <xm:sqref>M2:M18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70045B5F-E47C-405F-A775-F6297E3169F8}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$G$2:$G$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P17</xm:sqref>
+          <xm:sqref>P2:P18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{325ED70B-C71E-44AE-ACB0-7CBC2A62CC68}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W17</xm:sqref>
+          <xm:sqref>X2:X3 X5:X18 W4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3E52EC3F-BAF3-432C-80B7-E7CF91F212F2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X17</xm:sqref>
+          <xm:sqref>Y2:Y3 Y5:Y18 X4:Y4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CA7A5B91-E753-43AA-BCD2-EDBCB8C0F3B8}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y17</xm:sqref>
+          <xm:sqref>Z2:Z18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3978224F-2A31-4BC1-BBC5-77FA18F8E70F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Z2:Z17</xm:sqref>
+          <xm:sqref>AA2:AA18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{243A7FAA-70D3-4652-A277-5D7DA63CC7ED}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2:AB17</xm:sqref>
+          <xm:sqref>AC2:AC18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B07FBFEB-EF24-4A8C-97B9-E0EE015143E1}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AC2:AC17</xm:sqref>
+          <xm:sqref>AD2:AD18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B8EACD91-9495-427C-9233-444D9FD09925}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AD2:AD17</xm:sqref>
+          <xm:sqref>AE2:AE18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{32E98D23-6881-4F09-9F55-E7FE3AB41CE6}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$H$2:$H$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>U2:U17</xm:sqref>
+          <xm:sqref>U2:U18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{1EBD6FBA-5C7A-431C-B190-346B7D0C5C00}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>V2:V17</xm:sqref>
+          <xm:sqref>W2:W3 W5:W18</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DAC1FA14-7DD2-41AA-A08B-174B2E729693}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$I$2:$I$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
